--- a/metodos_aprovados/Validacao_Forward_Lay_Away_32_Jogos_Streamlit.xlsx
+++ b/metodos_aprovados/Validacao_Forward_Lay_Away_32_Jogos_Streamlit.xlsx
@@ -449,6 +449,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/metodos_aprovados/Validacao_Forward_Lay_Away_32_Jogos_Streamlit.xlsx
+++ b/metodos_aprovados/Validacao_Forward_Lay_Away_32_Jogos_Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_7E75F0DC5E75080E62355476585DCE3A8747DC60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E089AC-079D-49DD-A122-7400182D6471}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_7E75F0DC5E75080E62355476585DCE3A8747DC60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D880AA82-6759-4521-8D25-E6B8D791CFF2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="111">
   <si>
     <t>Data</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>P/L</t>
+  </si>
+  <si>
+    <t>Método</t>
+  </si>
+  <si>
+    <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
   </si>
 </sst>
 </file>
@@ -740,13 +746,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,8 +786,11 @@
       <c r="K1" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -816,8 +825,11 @@
         <f>IF(J2=1,0.965/(E2-1),-1)</f>
         <v>7.1907600596125179E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -852,8 +864,11 @@
         <f t="shared" ref="K3:K33" si="0">IF(J3=1,0.965/(E3-1),-1)</f>
         <v>0.13328729281767954</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -888,8 +903,11 @@
         <f t="shared" si="0"/>
         <v>6.9225251076040176E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -924,8 +942,11 @@
         <f t="shared" si="0"/>
         <v>9.341723136495643E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -960,8 +981,11 @@
         <f t="shared" si="0"/>
         <v>7.4748257164988383E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -996,8 +1020,11 @@
         <f t="shared" si="0"/>
         <v>0.10722222222222222</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1032,8 +1059,11 @@
         <f t="shared" si="0"/>
         <v>0.1227735368956743</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1068,8 +1098,11 @@
         <f t="shared" si="0"/>
         <v>0.1261437908496732</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1137,11 @@
         <f t="shared" si="0"/>
         <v>0.17262969588550983</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1140,8 +1176,11 @@
         <f t="shared" si="0"/>
         <v>8.8940092165898613E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1176,8 +1215,11 @@
         <f t="shared" si="0"/>
         <v>8.4947183098591547E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1212,8 +1254,11 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1248,8 +1293,11 @@
         <f t="shared" si="0"/>
         <v>0.10722222222222222</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1284,8 +1332,11 @@
         <f t="shared" si="0"/>
         <v>0.11117511520737328</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1320,8 +1371,11 @@
         <f t="shared" si="0"/>
         <v>6.9225251076040176E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1356,8 +1410,11 @@
         <f t="shared" si="0"/>
         <v>0.17262969588550983</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1392,8 +1449,11 @@
         <f t="shared" si="0"/>
         <v>7.4748257164988383E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1428,8 +1488,11 @@
         <f t="shared" si="0"/>
         <v>0.12953020134228188</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -1464,8 +1527,11 @@
         <f t="shared" si="0"/>
         <v>0.11972704714640198</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -1500,8 +1566,11 @@
         <f t="shared" si="0"/>
         <v>9.341723136495643E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -1536,8 +1605,11 @@
         <f t="shared" si="0"/>
         <v>9.341723136495643E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -1572,8 +1644,11 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1608,8 +1683,11 @@
         <f t="shared" si="0"/>
         <v>9.8369011213047905E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -1644,8 +1722,11 @@
         <f t="shared" si="0"/>
         <v>0.11972704714640198</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1680,8 +1761,11 @@
         <f t="shared" si="0"/>
         <v>0.11668681983071343</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1716,8 +1800,11 @@
         <f t="shared" si="0"/>
         <v>0.1227735368956743</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1752,8 +1839,11 @@
         <f t="shared" si="0"/>
         <v>0.15539452495974235</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -1788,8 +1878,11 @@
         <f t="shared" si="0"/>
         <v>0.11972704714640198</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -1824,8 +1917,11 @@
         <f t="shared" si="0"/>
         <v>0.10376344086021504</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -1860,8 +1956,11 @@
         <f t="shared" si="0"/>
         <v>9.8369011213047905E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1896,8 +1995,11 @@
         <f t="shared" si="0"/>
         <v>0.10616061606160616</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1931,6 +2033,9 @@
       <c r="K33">
         <f t="shared" si="0"/>
         <v>0.10376344086021504</v>
+      </c>
+      <c r="L33" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
